--- a/repair/back/doc/estimate/periodic3.xlsx
+++ b/repair/back/doc/estimate/periodic3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>식</t>
   </si>
@@ -1861,6 +1861,12 @@
   <si>
     <t xml:space="preserve">다. 점 검 범 위  : </t>
   </si>
+  <si>
+    <t>동법 시행령 제8조에 따라</t>
+  </si>
+  <si>
+    <t>「시설물의 안전 및 유지관리에 관한 특별법」(이하 “시설물안전법”이라 한다) 제11조, 제12조 및</t>
+  </si>
 </sst>
 </file>
 
@@ -1938,7 +1944,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="141">
+  <fonts count="150">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2613,12 +2619,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF006100"/>
@@ -2683,6 +2683,63 @@
       <color rgb="FF000000"/>
     </font>
     <font>
+      <b/>
+      <sz val="14.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <name val="돋움"/>
       <color rgb="FF000000"/>
@@ -2694,8 +2751,8 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
-      <name val="맑은 고딕"/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -4152,7 +4209,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4161,7 +4217,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4170,7 +4225,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4179,7 +4233,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4194,7 +4247,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4209,7 +4261,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -4224,7 +4275,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4233,7 +4283,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4244,7 +4293,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3161">
@@ -13686,19 +13734,19 @@
     <xf numFmtId="0" fontId="124" fillId="0" borderId="113" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="114" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="114" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13707,10 +13755,10 @@
     <xf numFmtId="0" fontId="111" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13719,10 +13767,10 @@
     <xf numFmtId="0" fontId="111" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13731,10 +13779,10 @@
     <xf numFmtId="0" fontId="111" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13743,10 +13791,10 @@
     <xf numFmtId="0" fontId="111" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13755,10 +13803,10 @@
     <xf numFmtId="0" fontId="111" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13767,14 +13815,14 @@
     <xf numFmtId="0" fontId="111" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="128" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="394">
+  <cellXfs count="401">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -14948,6 +14996,27 @@
     </xf>
     <xf numFmtId="37" fontId="105" fillId="0" borderId="0" xfId="3112" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3162">
@@ -19120,7 +19189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D1:AH1597"/>
+  <dimension ref="D1:AF1597"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="1" max="3" style="87" width="8.78277800" customWidth="1" outlineLevel="0"/>
@@ -19129,11 +19198,10 @@
     <col min="13" max="31" style="87" width="3.33833334" customWidth="1" outlineLevel="0"/>
     <col min="32" max="32" style="87" width="2.33833334" customWidth="1" outlineLevel="0"/>
     <col min="33" max="259" style="87" width="6.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="260" max="260" style="87" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="261" max="16384" style="87" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="260" max="16384" style="87" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:34" s="93" customFormat="1" ht="42.000000" customHeight="1">
+    <row r="1" spans="4:31" s="93" customFormat="1" ht="42.000000" customHeight="1">
       <c r="D1" s="329" t="s">
         <v>82</v>
       </c>
@@ -19165,7 +19233,7 @@
       <c r="AD1" s="329"/>
       <c r="AE1" s="329"/>
     </row>
-    <row r="2" spans="4:34" s="93" customFormat="1" ht="12.000000" customHeight="1">
+    <row r="2" spans="4:31" s="93" customFormat="1" ht="12.000000" customHeight="1">
       <c r="D2" s="138"/>
       <c r="E2" s="138"/>
       <c r="F2" s="138"/>
@@ -19195,7 +19263,7 @@
       <c r="AD2" s="139"/>
       <c r="AE2" s="139"/>
     </row>
-    <row r="3" spans="4:34" s="93" customFormat="1" ht="18.000000" customHeight="1">
+    <row r="3" spans="4:31" s="93" customFormat="1" ht="18.000000" customHeight="1">
       <c r="D3" s="330" t="s">
         <v>180</v>
       </c>
@@ -19227,7 +19295,7 @@
       <c r="AD3" s="330"/>
       <c r="AE3" s="330"/>
     </row>
-    <row r="4" spans="4:34" s="93" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="4" spans="4:31" s="93" customFormat="1" ht="7.500000" customHeight="1">
       <c r="D4" s="140"/>
       <c r="E4" s="140"/>
       <c r="F4" s="140"/>
@@ -19257,7 +19325,7 @@
       <c r="AD4" s="141"/>
       <c r="AE4" s="141"/>
     </row>
-    <row r="5" spans="4:34" s="93" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="5" spans="4:31" s="93" customFormat="1" ht="5.000000" customHeight="1">
       <c r="D5" s="138"/>
       <c r="E5" s="138"/>
       <c r="F5" s="138"/>
@@ -19287,7 +19355,7 @@
       <c r="AD5" s="139"/>
       <c r="AE5" s="139"/>
     </row>
-    <row r="6" spans="4:34" s="93" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="6" spans="4:31" s="93" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D6" s="148" t="s">
         <v>81</v>
       </c>
@@ -19321,7 +19389,7 @@
       <c r="AD6" s="138"/>
       <c r="AE6" s="138"/>
     </row>
-    <row r="7" spans="4:34" s="93" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="7" spans="4:31" s="93" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D7" s="148" t="s">
         <v>79</v>
       </c>
@@ -19355,7 +19423,7 @@
       <c r="AD7" s="138"/>
       <c r="AE7" s="138"/>
     </row>
-    <row r="8" spans="4:34" s="93" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="8" spans="4:31" s="93" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D8" s="148" t="s">
         <v>78</v>
       </c>
@@ -19389,7 +19457,7 @@
       <c r="AD8" s="331"/>
       <c r="AE8" s="331"/>
     </row>
-    <row r="9" spans="4:34" s="93" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="9" spans="4:31" s="93" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D9" s="148" t="s">
         <v>77</v>
       </c>
@@ -19401,32 +19469,8 @@
       </c>
       <c r="I9" s="142"/>
       <c r="J9" s="142"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="93"/>
-      <c r="S9" s="93"/>
-      <c r="T9" s="93"/>
-      <c r="U9" s="93"/>
-      <c r="V9" s="93"/>
-      <c r="W9" s="93"/>
-      <c r="X9" s="93"/>
-      <c r="Y9" s="93"/>
-      <c r="Z9" s="93"/>
-      <c r="AA9" s="93"/>
-      <c r="AB9" s="93"/>
-      <c r="AC9" s="93"/>
-      <c r="AD9" s="93"/>
-      <c r="AE9" s="93"/>
-      <c r="AF9" s="93"/>
-      <c r="AG9" s="93"/>
-      <c r="AH9" s="93"/>
-    </row>
-    <row r="10" spans="4:34" s="93" customFormat="1" ht="20.000000" customHeight="1">
+    </row>
+    <row r="10" spans="4:31" s="93" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D10" s="148" t="s">
         <v>75</v>
       </c>
@@ -19460,7 +19504,7 @@
       <c r="AD10" s="331"/>
       <c r="AE10" s="331"/>
     </row>
-    <row r="11" spans="4:34" s="93" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
+    <row r="11" spans="4:31" s="93" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="D11" s="143"/>
       <c r="E11" s="143"/>
       <c r="F11" s="143"/>
@@ -19490,7 +19534,7 @@
       <c r="AD11" s="143"/>
       <c r="AE11" s="143"/>
     </row>
-    <row r="12" spans="4:34" s="93" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="12" spans="4:31" s="93" customFormat="1" ht="7.500000" customHeight="1">
       <c r="D12" s="140"/>
       <c r="E12" s="140"/>
       <c r="F12" s="140"/>
@@ -19520,7 +19564,7 @@
       <c r="AD12" s="140"/>
       <c r="AE12" s="140"/>
     </row>
-    <row r="13" spans="4:34" s="93" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="13" spans="4:31" s="93" customFormat="1" ht="5.000000" customHeight="1">
       <c r="D13" s="138"/>
       <c r="E13" s="138"/>
       <c r="F13" s="138"/>
@@ -19550,7 +19594,7 @@
       <c r="AD13" s="138"/>
       <c r="AE13" s="138"/>
     </row>
-    <row r="14" spans="4:34" s="93" customFormat="1" ht="16.000000" customHeight="1">
+    <row r="14" spans="4:31" s="93" customFormat="1" ht="16.000000" customHeight="1">
       <c r="D14" s="149" t="s">
         <v>241</v>
       </c>
@@ -19582,7 +19626,7 @@
       <c r="AD14" s="149"/>
       <c r="AE14" s="149"/>
     </row>
-    <row r="15" spans="4:34" s="93" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="15" spans="4:31" s="93" customFormat="1" ht="5.000000" customHeight="1">
       <c r="D15" s="138"/>
       <c r="E15" s="138"/>
       <c r="F15" s="138"/>
@@ -19612,7 +19656,7 @@
       <c r="AD15" s="138"/>
       <c r="AE15" s="138"/>
     </row>
-    <row r="16" spans="4:34" s="93" customFormat="1" ht="60.000000" customHeight="1">
+    <row r="16" spans="4:31" s="93" customFormat="1" ht="60.000000" customHeight="1">
       <c r="D16" s="150" t="s">
         <v>242</v>
       </c>
@@ -34562,10 +34606,10 @@
     <mergeCell ref="D20:M20"/>
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="N21:AE21"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H23:M23"/>
     <mergeCell ref="N23:AE23"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H24:M24"/>
     <mergeCell ref="N24:AE24"/>
     <mergeCell ref="H25:M25"/>
@@ -34689,9 +34733,9 @@
         <v>70</v>
       </c>
       <c r="C5" s="355"/>
-      <c r="D5" s="356" t="e">
+      <c r="D5" s="356">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="356"/>
       <c r="F5" s="356"/>
@@ -46575,49 +46619,49 @@
       <c r="I59" s="9"/>
     </row>
     <row r="60" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B60" s="246" t="s">
-        <v>235</v>
+      <c r="B60" s="249" t="s">
+        <v>261</v>
       </c>
-      <c r="C60" s="246"/>
-      <c r="D60" s="246"/>
-      <c r="E60" s="246"/>
-      <c r="F60" s="246"/>
-      <c r="G60" s="246"/>
-      <c r="H60" s="246"/>
-      <c r="I60" s="246"/>
-      <c r="J60" s="246"/>
-      <c r="K60" s="246"/>
-      <c r="L60" s="246"/>
-      <c r="M60" s="246"/>
-      <c r="N60" s="246"/>
-      <c r="O60" s="246"/>
-      <c r="P60" s="246"/>
-      <c r="Q60" s="246"/>
-      <c r="R60" s="246"/>
-      <c r="S60" s="246"/>
-      <c r="T60" s="246"/>
-      <c r="U60" s="246"/>
+      <c r="C60" s="249"/>
+      <c r="D60" s="249"/>
+      <c r="E60" s="249"/>
+      <c r="F60" s="249"/>
+      <c r="G60" s="249"/>
+      <c r="H60" s="249"/>
+      <c r="I60" s="249"/>
+      <c r="J60" s="249"/>
+      <c r="K60" s="249"/>
+      <c r="L60" s="249"/>
+      <c r="M60" s="249"/>
+      <c r="N60" s="249"/>
+      <c r="O60" s="249"/>
+      <c r="P60" s="249"/>
+      <c r="Q60" s="249"/>
+      <c r="R60" s="249"/>
+      <c r="S60" s="249"/>
+      <c r="T60" s="249"/>
+      <c r="U60" s="249"/>
     </row>
     <row r="61" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B61" s="247" t="s">
-        <v>236</v>
+      <c r="B61" s="397" t="s">
+        <v>260</v>
       </c>
-      <c r="C61" s="247"/>
-      <c r="D61" s="247"/>
-      <c r="E61" s="247"/>
-      <c r="F61" s="247"/>
-      <c r="G61" s="247"/>
-      <c r="H61" s="247"/>
-      <c r="I61" s="247"/>
-      <c r="J61" s="248" t="str">
+      <c r="C61" s="397"/>
+      <c r="D61" s="397"/>
+      <c r="E61" s="397"/>
+      <c r="F61" s="397"/>
+      <c r="G61" s="397"/>
+      <c r="H61" s="397"/>
+      <c r="I61" s="400" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="K61" s="248"/>
-      <c r="L61" s="248"/>
-      <c r="M61" s="248"/>
-      <c r="N61" s="248"/>
-      <c r="O61" s="248"/>
+      <c r="J61" s="400"/>
+      <c r="K61" s="400"/>
+      <c r="L61" s="400"/>
+      <c r="M61" s="400"/>
+      <c r="N61" s="400"/>
+      <c r="O61" s="400"/>
       <c r="P61" s="247" t="s">
         <v>238</v>
       </c>
@@ -46628,28 +46672,28 @@
       <c r="U61" s="247"/>
     </row>
     <row r="62" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B62" s="246" t="s">
+      <c r="B62" s="249" t="s">
         <v>237</v>
       </c>
-      <c r="C62" s="246"/>
-      <c r="D62" s="246"/>
-      <c r="E62" s="246"/>
-      <c r="F62" s="246"/>
-      <c r="G62" s="246"/>
-      <c r="H62" s="246"/>
-      <c r="I62" s="246"/>
-      <c r="J62" s="246"/>
-      <c r="K62" s="246"/>
-      <c r="L62" s="246"/>
-      <c r="M62" s="246"/>
-      <c r="N62" s="246"/>
-      <c r="O62" s="246"/>
-      <c r="P62" s="246"/>
-      <c r="Q62" s="246"/>
-      <c r="R62" s="246"/>
-      <c r="S62" s="246"/>
-      <c r="T62" s="246"/>
-      <c r="U62" s="246"/>
+      <c r="C62" s="249"/>
+      <c r="D62" s="249"/>
+      <c r="E62" s="249"/>
+      <c r="F62" s="249"/>
+      <c r="G62" s="249"/>
+      <c r="H62" s="249"/>
+      <c r="I62" s="249"/>
+      <c r="J62" s="249"/>
+      <c r="K62" s="249"/>
+      <c r="L62" s="249"/>
+      <c r="M62" s="249"/>
+      <c r="N62" s="249"/>
+      <c r="O62" s="249"/>
+      <c r="P62" s="249"/>
+      <c r="Q62" s="249"/>
+      <c r="R62" s="249"/>
+      <c r="S62" s="249"/>
+      <c r="T62" s="249"/>
+      <c r="U62" s="249"/>
     </row>
     <row r="63" spans="2:21" ht="20.000000" customHeight="1">
       <c r="B63" s="108"/>
@@ -46754,7 +46798,7 @@
     </row>
     <row r="69" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C69" s="107" t="str">
-        <f>"② 위      치 : "&amp;E55</f>
+        <f>"② 위      치 : "&amp;갑지!N22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D69" s="107"/>
@@ -48876,8 +48920,8 @@
     <mergeCell ref="B57:U57"/>
     <mergeCell ref="B58:U58"/>
     <mergeCell ref="B60:U60"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="J61:O61"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="I61:O61"/>
     <mergeCell ref="P61:U61"/>
     <mergeCell ref="B62:U62"/>
     <mergeCell ref="B64:J64"/>

--- a/repair/back/doc/estimate/periodic3.xlsx
+++ b/repair/back/doc/estimate/periodic3.xlsx
@@ -1944,7 +1944,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="150">
+  <fonts count="153">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2753,6 +2753,22 @@
       <b/>
       <sz val="24.0"/>
       <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -45336,8 +45352,8 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="36" man="1"/>
     <brk id="9" max="1048575" man="1"/>
-    <brk id="9" max="36" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -48456,8 +48472,8 @@
       </c>
       <c r="Q147" s="85"/>
       <c r="R147" s="308">
-        <f>R138*P147%</f>
-        <v>109268.6</v>
+        <f>ROUND(R138*P147%,0)</f>
+        <v>109269</v>
       </c>
       <c r="S147" s="308"/>
       <c r="T147" s="308"/>
@@ -48490,8 +48506,8 @@
       </c>
       <c r="Q148" s="85"/>
       <c r="R148" s="311">
-        <f>(R138+R147)*P148%</f>
-        <v>120195.46</v>
+        <f>ROUND((R138+R147)*P148%,0)</f>
+        <v>120196</v>
       </c>
       <c r="S148" s="311"/>
       <c r="T148" s="311"/>
@@ -48517,7 +48533,7 @@
       <c r="P149" s="4"/>
       <c r="Q149" s="4"/>
       <c r="R149" s="315">
-        <f>SUM(R151:R155)</f>
+        <f>INT(SUM(R151:R155))</f>
         <v>219268</v>
       </c>
       <c r="S149" s="315"/>
@@ -48728,7 +48744,7 @@
       <c r="Q157" s="85"/>
       <c r="R157" s="327">
         <f>R138+R147+R148+R149</f>
-        <v>1541418.06</v>
+        <v>1541419</v>
       </c>
       <c r="S157" s="327"/>
       <c r="T157" s="327"/>
